--- a/🌟UNITED🌟.xlsx
+++ b/🌟UNITED🌟.xlsx
@@ -149,7 +149,7 @@
     <t>Hakim</t>
   </si>
   <si>
-    <t>Murtuza</t>
+    <t>Murtaza</t>
   </si>
   <si>
     <t>Grand Total</t>
